--- a/BuiThiNgocTran_Day22_model.xlsx
+++ b/BuiThiNgocTran_Day22_model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-20K-Phase2\Track1_Day22_2A202602529_BuiThiNgocTran\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC236049-EBA3-473D-B6F1-79EC781906F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C9FAE5B-81F5-4296-8D74-503382F219ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2076" yWindow="2556" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_README" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="538">
   <si>
     <t>DAY 22 — MONETIZATION MODEL</t>
   </si>
@@ -158,7 +158,7 @@
     <t>Bạn PHẢI tự mở lại trang giá của nhà cung cấp và cập nhật — đây là một phần của bài tập.</t>
   </si>
   <si>
-    <t>V5 RESEARCH SIMULATION · No MVP / customer interviews / payment or eval. 11_Simulations &amp; 12_Research_Sources contain scenarios and source trace; DO NOT report these as observed evidence.</t>
+    <t>PHẠM VI FILE: đúng 7 tab theo template gốc (0_README, 1_Cost_Job, 2_Pricing, 3_Value_Metric, 4_Channel_Fit, 5_90Day_Plan, 6_Benchmarks). Mô phỏng pre-MVP, không có Eval/pilot quan sát.</t>
   </si>
   <si>
     <t>OWNER / Người làm bài: Bùi Thị Ngọc Trân · dự án cá nhân. Mọi vai trò kỹ thuật/QA/Procurement trong kế hoạch đều do chủ dự án quản lý; chưa có nhân viên hay pilot.</t>
@@ -167,6 +167,51 @@
     <t>Dữ liệu giả định (containment 65%, CAC PLG $80, volume 1000 ticket, pricing) KHÔNG là kết quả thực nghiệm. Giá API 08/10/2026 cần tái xác minh khi nộp.</t>
   </si>
   <si>
+    <t>AI CRITIQUE LOG — 2 phản biện §4.7 (AI phân tích từ giả định; quyết định sửa cần người làm bài xác nhận)</t>
+  </si>
+  <si>
+    <t>§4.7.1 Cost/Job Stress Test</t>
+  </si>
+  <si>
+    <t>Phản biện: Nếu chỉ dựa vào containment 65%, thiếu eval; chi phí QA và retry có thể tăng.</t>
+  </si>
+  <si>
+    <t>§4.7.1 Kết quả</t>
+  </si>
+  <si>
+    <t>ACCEPT đề xuất: thêm kịch bản containment 45% và tỷ lệ QA cao; giữ HITL A, phải đo QA và retry khi pilot.</t>
+  </si>
+  <si>
+    <t>§4.7.1 Kiểm chứng</t>
+  </si>
+  <si>
+    <t>Tính toán stress test trong Pricing; không tuyên bố đây là dữ liệu thật. Quyết định accept đang là đề xuất để học viên xác nhận.</t>
+  </si>
+  <si>
+    <t>§4.7.3 Channel Reality Check</t>
+  </si>
+  <si>
+    <t>Phản biện: PLG chưa được chứng minh cho ARPU $178.5; API Zalo OA và conversion còn bất định.</t>
+  </si>
+  <si>
+    <t>§4.7.3 Kết quả</t>
+  </si>
+  <si>
+    <t>PARTIAL đề xuất: giữ PLG duy nhất cho 90 ngày vì sales-led CAC giả định vượt CAC budget 16,21 lần; chưa gọi CAC PLG $80 là quan sát.</t>
+  </si>
+  <si>
+    <t>§4.7.3 Kiểm chứng</t>
+  </si>
+  <si>
+    <t>Tính CAC budget, cost/opportunity và deal/AE/day trong Channel_Fit; điều kiện dừng: measured CAC &gt; budget hoặc không được cấp quyền OA.</t>
+  </si>
+  <si>
+    <t>Trạng thái log</t>
+  </si>
+  <si>
+    <t>AI đã thực hiện phản biện trên số giả định; accept/partial là gợi ý, chủ bài cần đọc và tự xác nhận.</t>
+  </si>
+  <si>
     <t>TAB 1 — COST/JOB CALCULATOR</t>
   </si>
   <si>
@@ -1100,7 +1145,7 @@
     <t>Việc cụ thể 1</t>
   </si>
   <si>
-    <t>15 phỏng vấn, xác thực volume + workflow</t>
+    <t>Nghiên cứu nguồn công khai, thiết kế bảng phỏng vấn; 15 phỏng vấn là mục tiêu khi có điều kiện, CHƯA THỰC HIỆN</t>
   </si>
   <si>
     <t>Đưa MVP sandbox, đo ticket outcome</t>
@@ -1124,7 +1169,7 @@
     <t>Việc cụ thể 3</t>
   </si>
   <si>
-    <t>Thu 100 hội thoại giả lập, có đồng ý</t>
+    <t>Thiết kế 100 tình huống eval tổng hợp; không sử dụng hội thoại khách hàng thật khi chưa có consent</t>
   </si>
   <si>
     <t>1000+ ticket pilot đã gắn nhãn</t>
@@ -1136,7 +1181,7 @@
     <t>KPI đo được</t>
   </si>
   <si>
-    <t>15 interview + 5 shops đồng thiết kế + 100 tình huống eval (TARGET)</t>
+    <t>Đầu ra tài liệu: 100 case thiết kế, 2 benchmark có link; 5 shop discovery là mục tiêu chưa thực hiện</t>
   </si>
   <si>
     <t>10 shop kích hoạt; 3 pilot mục tiêu; &gt;=60% containment chỉ nếu đo đúng</t>
@@ -1178,37 +1223,37 @@
     <t>1. Eval Results</t>
   </si>
   <si>
-    <t>CHƯA CÓ — cần tạo bộ eval</t>
-  </si>
-  <si>
-    <t>Eval 100 case phân tầng 4 intent; accuracy, unsupported claim, escalation, 24h-reopen, audit sampling</t>
-  </si>
-  <si>
-    <t>Bùi Thị Ngọc Trân · deadline 31/10/2026 (kế hoạch, chưa có Eval)</t>
+    <t>CHƯA CÓ — kế hoạch Eval</t>
+  </si>
+  <si>
+    <t>Bộ 100 case đo containment và policy compliance; không báo số thành công trước khi chạy.</t>
+  </si>
+  <si>
+    <t>Bùi Thị Ngọc Trân · 31/10/2026 (dự kiến)</t>
   </si>
   <si>
     <t>2. Risk Checklist</t>
   </si>
   <si>
-    <t>CHƯA CÓ — cần procurement Q&amp;A</t>
-  </si>
-  <si>
-    <t>Q&amp;A có trích tài liệu thực tế nhà cung cấp: train-data, retention, DPA, export/delete, thất bại &amp; fallback</t>
-  </si>
-  <si>
-    <t>Bùi Thị Ngọc Trân · deadline 15/11/2026 (Q&amp;A dạng draft; cần đối chiếu điều khoản DPA/retention)</t>
+    <t>BẢN NHÁP — cần xác minh</t>
+  </si>
+  <si>
+    <t>Procurement Q&amp;A: hallucination / data train / export-delete; đối chiếu hợp đồng, DPA, quyền API.</t>
+  </si>
+  <si>
+    <t>Bùi Thị Ngọc Trân · 15/11/2026 (dự kiến)</t>
   </si>
   <si>
     <t>3. Pilot Report</t>
   </si>
   <si>
-    <t>CHƯA CÓ — cần thử pilot; không giả định hợp đồng</t>
-  </si>
-  <si>
-    <t>Pilot 4 tuần tại 3 shop CÓ CONSENT; báo cáo 1000+ ticket, thời gian tiết kiệm thực, CAC, invoice (nếu có)</t>
-  </si>
-  <si>
-    <t>Bùi Thị Ngọc Trân · deadline 08/01/2027 (pilot chưa thực hiện)</t>
+    <t>CHƯA CÓ — kế hoạch Pilot</t>
+  </si>
+  <si>
+    <t>Mục tiêu pilot 4 tuần, 3 shop có đồng ý, 1.000+ ticket nếu có MVP; chưa thu thập kết quả.</t>
+  </si>
+  <si>
+    <t>Bùi Thị Ngọc Trân · 08/01/2027 (dự kiến)</t>
   </si>
   <si>
     <t>Ô nào CHƯA CÓ thì ghi deadline — đừng bỏ trống. Thành thật về khoảng trống được điểm cao hơn bịa nội dung.</t>
@@ -1871,7 +1916,7 @@
         <xdr:cNvPr id="1026" name="Text Box 2" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4707471-7BC5-460D-9597-B8620CD4E2E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29977838-D760-474D-80F8-CAE19689C866}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2216,73 +2261,126 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:1" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3254,7 +3352,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3266,12 +3364,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -3283,29 +3381,29 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -3317,62 +3415,62 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B9" s="15">
         <v>1000</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B10" s="16">
         <v>0.65</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B11" s="19">
         <f>B9*B10</f>
         <v>650</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B12" s="19">
         <f>B9-B11</f>
         <v>350</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -3384,18 +3482,18 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B15" s="22">
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B16" s="22">
         <v>5</v>
@@ -3403,79 +3501,79 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B17" s="22">
         <v>1.25</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B18" s="22">
         <v>0.1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B19" s="15">
         <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B20" s="15">
         <v>3000</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B21" s="15">
         <v>1000</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B22" s="15">
         <v>300</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B23" s="24">
         <f>B20*B17/1000000</f>
@@ -3484,7 +3582,7 @@
     </row>
     <row r="24" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B24" s="24">
         <f>(B19-1)*B20*B18/1000000</f>
@@ -3493,7 +3591,7 @@
     </row>
     <row r="25" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B25" s="24">
         <f>B19*B21*B15/1000000</f>
@@ -3502,7 +3600,7 @@
     </row>
     <row r="26" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B26" s="24">
         <f>B19*B22*B16/1000000</f>
@@ -3511,7 +3609,7 @@
     </row>
     <row r="27" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B27" s="23">
         <f>SUM(B23:B26)</f>
@@ -3520,7 +3618,7 @@
     </row>
     <row r="28" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B28" s="24">
         <f>B19*(B20+B21)*B15/1000000+B26</f>
@@ -3529,30 +3627,30 @@
     </row>
     <row r="29" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B29" s="28">
         <f>IF(B28=0,0,1-B27/B28)</f>
         <v>0.38636363636363646</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="B30" s="15">
         <v>0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B31" s="23">
         <f>B27*(1-B30*0.5)</f>
@@ -3562,7 +3660,7 @@
     <row r="32" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -3574,54 +3672,54 @@
     </row>
     <row r="34" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B34" s="29">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="B35" s="21">
         <v>0</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B36" s="22">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B37" s="15">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B38" s="24">
         <f>B34*B35+B36*B37/1000000</f>
@@ -3631,7 +3729,7 @@
     <row r="39" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
@@ -3643,29 +3741,29 @@
     </row>
     <row r="41" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B41" s="29">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B42" s="29">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B43" s="24">
         <f>B41+B42*B35</f>
@@ -3675,7 +3773,7 @@
     <row r="44" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -3687,18 +3785,18 @@
     </row>
     <row r="46" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B46" s="16">
         <v>0.1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B47" s="24">
         <f>(B31+B38)*B46</f>
@@ -3708,7 +3806,7 @@
     <row r="48" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
@@ -3720,51 +3818,51 @@
     </row>
     <row r="50" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B50" s="22">
         <v>8</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B51" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B52" s="21">
         <v>2</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B53" s="21">
         <v>6</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B54" s="32">
         <f>B9*B51*(B52/60)*B50</f>
@@ -3773,19 +3871,19 @@
     </row>
     <row r="55" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B55" s="32">
         <f>IF(B6="B",B12*(B53/60)*B50,0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B56" s="33">
         <f>B54+B55</f>
@@ -3795,7 +3893,7 @@
     <row r="57" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -3807,23 +3905,23 @@
     </row>
     <row r="59" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B59" s="22">
         <v>40</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
@@ -3835,7 +3933,7 @@
     </row>
     <row r="62" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B62" s="32">
         <f>B9*(B31+B38+B43+B47)</f>
@@ -3844,7 +3942,7 @@
     </row>
     <row r="63" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B63" s="32">
         <f>B56</f>
@@ -3853,7 +3951,7 @@
     </row>
     <row r="64" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B64" s="32">
         <f>B59</f>
@@ -3862,78 +3960,78 @@
     </row>
     <row r="65" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B65" s="32">
         <f>B62+B63+B64</f>
         <v>88.941666666666663</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B66" s="23">
         <f>IF(B11=0,0,(B62+B63)/B11)</f>
         <v>7.5294871794871793E-2</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B67" s="23">
         <f>IF(B11=0,0,B65/B11)</f>
         <v>0.13683333333333333</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B68" s="15">
         <v>26000</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="B69" s="36">
         <f>B66*B68</f>
         <v>1957.6666666666665</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="10"/>
@@ -3942,7 +4040,7 @@
     </row>
     <row r="72" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B72" s="32">
         <f>B9*B31</f>
@@ -3955,7 +4053,7 @@
     </row>
     <row r="73" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B73" s="32">
         <f>B9*B38</f>
@@ -3968,7 +4066,7 @@
     </row>
     <row r="74" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B74" s="32">
         <f>B9*B43</f>
@@ -3981,7 +4079,7 @@
     </row>
     <row r="75" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B75" s="32">
         <f>B9*B47</f>
@@ -3994,7 +4092,7 @@
     </row>
     <row r="76" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B76" s="32">
         <f>B56</f>
@@ -4007,7 +4105,7 @@
     </row>
     <row r="77" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B77" s="32">
         <f>B59</f>
@@ -4020,7 +4118,7 @@
     </row>
     <row r="78" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4971,7 +5069,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4983,12 +5081,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -4996,23 +5094,23 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B5" s="20">
         <f>'1_Cost_Job'!B66</f>
         <v>7.5294871794871793E-2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="H5">
         <v>29</v>
@@ -5020,19 +5118,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B6" s="21">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="G6" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="H6">
         <v>0.23</v>
@@ -5040,17 +5138,17 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B7" s="23">
         <f>B5*B6</f>
         <v>0.22588461538461538</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H7">
         <f>'1_Cost_Job'!B11</f>
@@ -5059,7 +5157,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G8" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="H8">
         <f>H5+H6*H7</f>
@@ -5068,7 +5166,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -5076,7 +5174,7 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="H9" s="10">
         <f>'1_Cost_Job'!B62+'1_Cost_Job'!B63</f>
@@ -5085,16 +5183,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B10" s="25">
         <v>850</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H10">
         <f>IF(H8=0,0,1-H9/H8)</f>
@@ -5103,17 +5201,17 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B11" s="15">
         <f>'1_Cost_Job'!B11</f>
         <v>650</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="H11">
         <f>H8</f>
@@ -5122,17 +5220,17 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B12" s="24">
         <f>IF(B11=0,0,B10*0.1/B11)</f>
         <v>0.13076923076923078</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H12">
         <f>IF(H7=0,0,H8/H7)</f>
@@ -5141,17 +5239,17 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B13" s="24">
         <f>IF(B11=0,0,B10*0.25/B11)</f>
         <v>0.32692307692307693</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="H13">
         <f>'1_Cost_Job'!B64</f>
@@ -5160,16 +5258,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B14" s="25">
         <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="G14" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H14">
         <f>H8-H9-H13</f>
@@ -5178,17 +5276,17 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B15" s="24">
         <f>IF(B11=0,0,B14*0.5/B11)</f>
         <v>0.34615384615384615</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G15" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="H15">
         <f>IF(H5+H6*'1_Cost_Job'!B9*0.5=0,0,1-('1_Cost_Job'!B9*($B$29+$B$30+$B$31*(1-0.5)))/(H5+H6*'1_Cost_Job'!B9*0.5))</f>
@@ -5197,17 +5295,17 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B16" s="24">
         <f>IF(B11=0,0,B14*0.7/B11)</f>
         <v>0.48461538461538461</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G16" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H16">
         <f>MAX(0,('1_Cost_Job'!B9*($B$29+$B$30+$B$31)-(1-0.5)*H5)/('1_Cost_Job'!B9*((1-0.5)*H6+$B$31)))</f>
@@ -5216,7 +5314,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G17" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="H17">
         <f>H10</f>
@@ -5225,7 +5323,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -5233,7 +5331,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="H18" s="10">
         <f>IF(H8=0,0,H5/H8)</f>
@@ -5242,20 +5340,20 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B19" s="29">
         <f>H12</f>
         <v>0.27461538461538459</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G19" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="H19">
         <f>IF(B10=0,0,H8/B10)</f>
@@ -5264,7 +5362,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B20" s="30">
         <f>IF(B5=0,0,B19/B5)</f>
@@ -5273,71 +5371,71 @@
     </row>
     <row r="21" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B21" s="31">
         <f>H10</f>
         <v>0.72581699346405237</v>
       </c>
       <c r="D21" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="G21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="B22" s="8" t="str">
         <f>IF(B20&gt;=B6,"OK — ĐẠT","KHÔNG ĐẠT — quay lại tab 1")</f>
         <v>OK — ĐẠT</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B23" s="8" t="str">
         <f>IF(B21&gt;=0.6,"OK — AN TOÀN (≥60%)",IF(B21&gt;=0.5,"CẢNH BÁO (50–60%)","NGUY HIỂM (&lt;50%)"))</f>
         <v>OK — AN TOÀN (≥60%)</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B24" s="8" t="str">
         <f>IF(B21&gt;0.85,"NGHI NGỜ — nhiều khả năng bạn quên một khoản chi phí","OK")</f>
         <v>OK</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B25" s="8" t="str">
         <f>IF(AND(B19&gt;=B7,B19&lt;=MAX(B13,B16)),"OK — trong vùng giá bán","XEM LẠI — ngoài vùng giá sàn/trần")</f>
         <v>OK — trong vùng giá bán</v>
       </c>
       <c r="G25" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -5349,12 +5447,12 @@
     </row>
     <row r="28" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B29" s="20">
         <f>'1_Cost_Job'!B31+'1_Cost_Job'!B38+'1_Cost_Job'!B43+'1_Cost_Job'!B47</f>
@@ -5363,7 +5461,7 @@
     </row>
     <row r="30" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B30" s="20">
         <f>'1_Cost_Job'!B51*('1_Cost_Job'!B52/60)*'1_Cost_Job'!B50</f>
@@ -5372,7 +5470,7 @@
     </row>
     <row r="31" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B31" s="20">
         <f>IF('1_Cost_Job'!B6="B",('1_Cost_Job'!B53/60)*'1_Cost_Job'!B50,0)</f>
@@ -5381,7 +5479,7 @@
     </row>
     <row r="32" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B32" s="16">
         <v>0.6</v>
@@ -5389,19 +5487,19 @@
     </row>
     <row r="33" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B33" s="31">
         <f>MAX(0,('1_Cost_Job'!B9*(B29+B30+B31)-(1-B32)*H5)/('1_Cost_Job'!B9*((1-B32)*H6+B31)))</f>
         <v>0.40588768115942014</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B34" s="34">
         <f>'1_Cost_Job'!B10</f>
@@ -5410,7 +5508,7 @@
     </row>
     <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B35" s="8" t="str">
         <f>IF(B34&gt;=B33,"ĐẠT — mô hình có lãi lành mạnh","CHƯA ĐẠT — phải tăng containment, tăng giá, hoặc đổi biến thể HITL")</f>
@@ -5420,7 +5518,7 @@
     <row r="36" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -5432,16 +5530,16 @@
     </row>
     <row r="38" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="27" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5543,13 +5641,13 @@
     <row r="45" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="48" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -5561,7 +5659,7 @@
     </row>
     <row r="49" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B49" s="23">
         <f>B5</f>
@@ -5570,7 +5668,7 @@
     </row>
     <row r="50" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B50" s="23">
         <f>B7</f>
@@ -5579,7 +5677,7 @@
     </row>
     <row r="51" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B51" s="23">
         <f>B19</f>
@@ -5588,7 +5686,7 @@
     </row>
     <row r="52" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B52" s="31">
         <f>B21</f>
@@ -5597,7 +5695,7 @@
     </row>
     <row r="53" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B53" s="31">
         <f>B33</f>
@@ -6571,7 +6669,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6583,12 +6681,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -6600,7 +6698,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B5" s="13">
         <v>0</v>
@@ -6608,7 +6706,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="B6" s="13">
         <v>0</v>
@@ -6616,7 +6714,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B7" s="13">
         <v>0</v>
@@ -6624,7 +6722,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="B8" s="13">
         <v>0</v>
@@ -6632,7 +6730,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="B9" s="13">
         <v>1</v>
@@ -6640,7 +6738,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="B10" s="18">
         <f>SUM(B5:B9)</f>
@@ -6649,7 +6747,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -6661,7 +6759,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B13" s="13">
         <v>0</v>
@@ -6669,7 +6767,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="B14" s="13">
         <v>0</v>
@@ -6677,7 +6775,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="B15" s="13">
         <v>0</v>
@@ -6685,7 +6783,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B16" s="13">
         <v>0</v>
@@ -6693,7 +6791,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B17" s="13">
         <v>0</v>
@@ -6701,7 +6799,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B18" s="18">
         <f>SUM(B13:B17)</f>
@@ -6710,7 +6808,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -6722,7 +6820,7 @@
     </row>
     <row r="21" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B21" s="26" t="str">
         <f>IF(AND(B10&gt;=7,B18&gt;=7),"OUTCOME",IF(AND(B10&gt;=7,B18&lt;7),"USAGE",IF(AND(B10&lt;7,B18&gt;=7),"USAGE (an toàn)","SEAT hoặc HYBRID")))</f>
@@ -6731,13 +6829,13 @@
     </row>
     <row r="22" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
@@ -6749,50 +6847,50 @@
     </row>
     <row r="25" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -6804,42 +6902,42 @@
     </row>
     <row r="30" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7827,7 +7925,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7839,12 +7937,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7852,20 +7950,20 @@
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B5" s="25">
         <f>'2_Pricing'!H11</f>
         <v>178.5</v>
       </c>
       <c r="G5" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="H5">
         <v>800</v>
@@ -7873,14 +7971,14 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="B6" s="34">
         <f>'2_Pricing'!B21</f>
         <v>0.72581699346405237</v>
       </c>
       <c r="G6" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="H6">
         <v>0.08</v>
@@ -7888,13 +7986,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G7" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="H7">
         <v>0.25</v>
@@ -7902,20 +8000,20 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B8" s="19">
         <f>IF(B7="SMB",12,IF(B7="Mid",18,24))</f>
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="G8" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="H8">
         <v>0.25</v>
@@ -7923,17 +8021,17 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B9" s="35">
         <f>B5*B6*B8</f>
         <v>1554.7</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="G9" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="H9">
         <f>H5*H6*H7*H8</f>
@@ -7942,14 +8040,14 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B10" s="37">
         <f>B5*12</f>
         <v>2142</v>
       </c>
       <c r="G10" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="H10">
         <v>240</v>
@@ -7957,7 +8055,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G11" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -7965,7 +8063,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -7973,7 +8071,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="H12" s="10">
         <f>IF(H9&lt;1,NA(),(H10+H11)/H9)</f>
@@ -7982,16 +8080,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="B13" s="25">
         <v>500000</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="G13" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H13">
         <f>IFERROR(B9/H12,0)</f>
@@ -8000,16 +8098,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B14" s="15">
         <v>250</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="G14" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="H14" t="str">
         <f>IFERROR(IF(H12&lt;=B9,"PASS hypothesis","FAIL hypothesis"),"NO DATA")</f>
@@ -8018,54 +8116,54 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B15" s="19">
         <f>IF(B10=0,0,B13/B10)</f>
         <v>233.4267040149393</v>
       </c>
       <c r="G15" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B16" s="38">
         <f>IF(B14=0,0,B15/B14)</f>
         <v>0.93370681605975725</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="G16" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B17" s="8" t="str">
         <f>IF(B16&lt;=1,"KHẢ THI về mặt số học","BẤT KHẢ THI — ACV quá thấp để nuôi sales rep")</f>
         <v>KHẢ THI về mặt số học</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="G17" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G18" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -8077,18 +8175,18 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="B20" s="25">
         <v>6300</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B21" s="16">
         <v>0.25</v>
@@ -8096,7 +8194,7 @@
     </row>
     <row r="22" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B22" s="37">
         <f>IF(B21=0,0,B20/B21)</f>
@@ -8105,19 +8203,19 @@
     </row>
     <row r="23" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B23" s="39">
         <f>IF(B9=0,0,B22/B9)</f>
         <v>16.208914903196757</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B24" s="8" t="str">
         <f>IF(B23&lt;=1,"Motion có sales KHẢ THI",IF(B23&lt;=3,"Căng — cần tăng giá hoặc giảm chi phí bán hàng","KHÔNG KHẢ THI — đi PLG hoặc Partner-Led"))</f>
@@ -8127,7 +8225,7 @@
     <row r="25" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -8139,21 +8237,21 @@
     </row>
     <row r="27" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="27" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B28" s="13">
         <v>4</v>
@@ -8167,7 +8265,7 @@
     </row>
     <row r="29" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B29" s="13">
         <v>3</v>
@@ -8181,7 +8279,7 @@
     </row>
     <row r="30" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B30" s="13">
         <v>3</v>
@@ -8195,7 +8293,7 @@
     </row>
     <row r="31" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B31" s="13">
         <v>3</v>
@@ -8209,7 +8307,7 @@
     </row>
     <row r="32" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B32" s="13">
         <v>4</v>
@@ -8223,7 +8321,7 @@
     </row>
     <row r="33" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B33" s="13">
         <v>4</v>
@@ -8237,7 +8335,7 @@
     </row>
     <row r="34" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B34" s="26">
         <f t="shared" ref="B34:D34" si="0">SUM(B28:B33)</f>
@@ -8254,7 +8352,7 @@
     </row>
     <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B35" s="26" t="str">
         <f>IF(AND(B34&gt;=C34,B34&gt;=D34),"PLG",IF(C34&gt;=D34,"Sales-Led","Partner-Led"))</f>
@@ -8264,7 +8362,7 @@
     <row r="36" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -8276,51 +8374,51 @@
     </row>
     <row r="38" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -9304,7 +9402,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9316,12 +9414,12 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -9333,42 +9431,42 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -9381,121 +9479,121 @@
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="27"/>
       <c r="B11" s="27" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -9507,72 +9605,72 @@
     </row>
     <row r="22" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="B24" s="41" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -9583,34 +9681,34 @@
     </row>
     <row r="29" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10602,7 +10700,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10614,669 +10712,669 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="42" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D7" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="D8" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A14" s="43" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="43" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="43" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="43" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="43" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="43" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="43" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="43" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="43" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="B23" s="43" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="43" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="43" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="43" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="D30" s="43" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C31" s="43" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="C32" s="43" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D32" s="43" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C33" s="43" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="43" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="C40" s="43" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="43" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="C41" s="43" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="43" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="E44" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="E45" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="12.6" customHeight="1" x14ac:dyDescent="0.3"/>
